--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MARYLAND_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MARYLAND_2014.xlsx
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C180">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C402">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C754">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C837">
